--- a/SampleData/Modern/NeotekEstatementsSampleRequestData.xlsx
+++ b/SampleData/Modern/NeotekEstatementsSampleRequestData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TFS\API Marketplace\Development\Core\Java-APIs\00-Source-Code\Marketplace Sandbox\MP Sandbox DB\Sample Request Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salseriea.EJADA\Desktop\MP\sumayyah\marketplace_latest 13\marketplace_latest\SampleData\Modern\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094DBD82-D30C-4086-87A4-02D1DFED1A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA704C3-B501-4F7D-BA42-31B64BCDEBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{50C03649-0042-4D5A-8BD6-E7242B0000F4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50C03649-0042-4D5A-8BD6-E7242B0000F4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="E-Statements" sheetId="1" r:id="rId1"/>
+    <sheet name="FinancialInstitutions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Field Name</t>
   </si>
@@ -123,13 +124,59 @@
   </si>
   <si>
     <t>AccountsLinkIds[0]</t>
+  </si>
+  <si>
+    <t>Modern Financial Institutions - Sample Request Data</t>
+  </si>
+  <si>
+    <t>List Financial Institutions</t>
+  </si>
+  <si>
+    <t>financialInstitutionId</t>
+  </si>
+  <si>
+    <t>INMASARI</t>
+  </si>
+  <si>
+    <t>RJHISARI</t>
+  </si>
+  <si>
+    <t>financialInstitutionName</t>
+  </si>
+  <si>
+    <t>SAMA Model Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       List Financial Institution DataGroups</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FinancialInstitutionId</t>
+    </r>
+  </si>
+  <si>
+    <t>BSFRSARI</t>
+  </si>
+  <si>
+    <t>SAMAModelBank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,8 +235,52 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -220,8 +311,14 @@
         <bgColor rgb="FFE8E8E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAE9F8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -352,11 +449,94 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -381,12 +561,27 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -396,19 +591,40 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -746,65 +962,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054A50EE-133C-4E21-872E-6189E0B098F4}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="6" width="30.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="6" width="30.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
       <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
@@ -821,15 +1037,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
       <c r="B5" s="8"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>19</v>
       </c>
@@ -849,15 +1065,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
       <c r="B7" s="8"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -877,15 +1093,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
       <c r="B9" s="8"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
@@ -905,7 +1121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="8"/>
       <c r="C11" s="2"/>
@@ -924,4 +1140,110 @@
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;KFFFF00 Ejada Internal Use Only</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00CE204-7E67-4BC5-9770-27F6FCEDE614}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="33"/>
+      <c r="B4" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0f1e79fc-1f4d-4187-a67d-c1c5354c13f8}" enabled="1" method="Standard" siteId="{e1304ad9-93ba-4557-8b20-8c1c1143b399}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>